--- a/perfiles.xlsx
+++ b/perfiles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72535BF-167D-408A-B3BC-D43C82748618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A603D1E-EE31-45BC-B3F7-179C08EB7DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1575" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -957,6 +957,9 @@
       <c r="K8" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="L8">
+        <v>170</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -989,6 +992,9 @@
       <c r="K9" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="L9">
+        <v>168</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1024,6 +1030,9 @@
       <c r="K10" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="L10">
+        <v>168</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1056,6 +1065,9 @@
       <c r="K11" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="L11">
+        <v>158</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1091,6 +1103,9 @@
       <c r="K12" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="L12">
+        <v>175</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1126,6 +1141,9 @@
       <c r="K13" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="L13">
+        <v>168</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1161,6 +1179,9 @@
       <c r="K14" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="L14">
+        <v>160</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1195,6 +1216,9 @@
       </c>
       <c r="K15" s="2" t="s">
         <v>54</v>
+      </c>
+      <c r="L15">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/perfiles.xlsx
+++ b/perfiles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A603D1E-EE31-45BC-B3F7-179C08EB7DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA29E0BB-EB7E-42CD-8CBE-B2E8C4118B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1575" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -849,7 +849,7 @@
         <v>54</v>
       </c>
       <c r="L5">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">

--- a/perfiles.xlsx
+++ b/perfiles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA29E0BB-EB7E-42CD-8CBE-B2E8C4118B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BF4342-3196-4741-BB19-5EE43B1ED413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1575" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
   <si>
     <t>Atleta</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>Altura_cm</t>
+  </si>
+  <si>
+    <t>DODODO</t>
   </si>
 </sst>
 </file>
@@ -719,6 +722,9 @@
       <c r="B2" t="s">
         <v>1</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="D2" s="2">
         <v>27</v>
       </c>
